--- a/reports/集团总公司_利润表_2025-03.xlsx
+++ b/reports/集团总公司_利润表_2025-03.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>219317745</v>
+        <v>238465762</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>166865299</v>
+        <v>180573484</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>460202004</v>
+        <v>498769741</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>677954</v>
+        <v>883297</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1876959</v>
+        <v>2430883</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>589044</v>
+        <v>773264</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1628035</v>
+        <v>2129645</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>497182</v>
+        <v>652610</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1376498</v>
+        <v>1799247</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>459485</v>
+        <v>601852</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1267420</v>
+        <v>1661401</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>248768</v>
+        <v>330501</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>687488</v>
+        <v>913528</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>200175</v>
+        <v>259963</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>551025</v>
+        <v>719239</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>216645137</v>
+        <v>234964275</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164192691</v>
+        <v>177071997</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84875233</v>
+        <v>92184777</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>233320653</v>
+        <v>255388258</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1556488</v>
+        <v>2741022</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4285190</v>
+        <v>7570435</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1406693</v>
+        <v>1993888</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3874219</v>
+        <v>5502602</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>74671801</v>
+        <v>78872728</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>206698008</v>
+        <v>217183196</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1608089</v>
+        <v>2001248</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4427794</v>
+        <v>5506954</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>697821</v>
+        <v>1002273</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1932664</v>
+        <v>2757676</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2510341</v>
+        <v>3012599</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>6914364</v>
+        <v>8285439</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1095321</v>
+        <v>1505971</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3034302</v>
+        <v>4145616</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>52282619</v>
+        <v>52412899</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>144337474</v>
+        <v>144921420</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169827</v>
+        <v>170424</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>509656</v>
+        <v>511575</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3187457</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8804815</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2121498</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5866880</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>158537322</v>
+        <v>179030871</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>127235120</v>
+        <v>133847446</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>100022426</v>
+        <v>106829864</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>275952784</v>
+        <v>295908587</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27212694</v>
+        <v>27017582</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>74906616</v>
+        <v>74481737</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5279248</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>14584923</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1691011</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4665787</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1058463</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2916919</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1272377</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3503098</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>955899</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2630425</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>638121</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1755992</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>532169</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1465215</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2933281</v>
+        <v>2960908</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8125852</v>
+        <v>8165766</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1389835</v>
+        <v>1396922</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3833906</v>
+        <v>3849205</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3586898</v>
+        <v>3596589</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>9918661</v>
+        <v>9955234</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>23313506</v>
+        <v>23246908</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>64282497</v>
+        <v>64361443</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349357</v>
+        <v>2835446</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1047160</v>
+        <v>7850704</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1119160</v>
+        <v>1116286</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3355817</v>
+        <v>3358833</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1163740</v>
+        <v>1067045</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3480953</v>
+        <v>3208594</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>119949</v>
+        <v>119493</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>359817</v>
+        <v>359290</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>475177</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1426736</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>924932</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2551612</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>317611</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>951172</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>238627</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>713962</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>398373</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1191361</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1329603</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3658977</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212878</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>637080</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159648</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>478281</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>265874</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>797550</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>185859</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>558260</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132532</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>398518</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105840</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>318479</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79263</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>238546</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>58107815</v>
+        <v>59195711</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>62950257</v>
+        <v>62897302</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>528029</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1458298</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132157</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>396206</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>209874</v>
+        <v>209790</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>630652</v>
+        <v>628189</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57897941</v>
+        <v>59513950</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7075137</v>
+        <v>7115908</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>21304038</v>
+        <v>21279512</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50822804</v>
+        <v>52398042</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50822804</v>
+        <v>52398042</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50822804</v>
+        <v>52398042</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50822804</v>
+        <v>52398042</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50822804</v>
+        <v>52398042</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
